--- a/repo/modelo-formandos.xlsx
+++ b/repo/modelo-formandos.xlsx
@@ -11,6 +11,9 @@
     <sheet sheetId="2" name="Listas" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Instruções" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Listas'!$A1:$E30</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -114,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Nome</t>
   </si>
@@ -140,13 +143,13 @@
     <t>Notas</t>
   </si>
   <si>
-    <t>Entidades</t>
+    <t>Escolas e entidades</t>
   </si>
   <si>
     <t>Cursos</t>
   </si>
   <si>
-    <t>Acrescenta aqui, por baixo dos que já existem. Escreve cada curso sempre da mesma maneira: é pelo nome que o Repo os reconhece.</t>
+    <t>Foste convidado para uma escola nova, ou vais dar um curso novo? Escreve-o aqui, por baixo dos que já existem.</t>
   </si>
   <si>
     <t>IEFP</t>
@@ -161,6 +164,9 @@
     <t>UFCD 10870</t>
   </si>
   <si>
+    <t>Sem linhas em branco pelo meio: a lista pára na primeira célula vazia. Escreve cada nome sempre da mesma maneira, porque é pelo nome que o Repo os reconhece.</t>
+  </si>
+  <si>
     <t>Como preencher</t>
   </si>
   <si>
@@ -170,7 +176,7 @@
     <t>2. Uma linha = uma pessoa numa formação. Se alguém fez três formações contigo, aparece em três linhas. É assim mesmo: o Repo junta-as pelo email.</t>
   </si>
   <si>
-    <t>3. Curso e Entidade escolhem-se da lista. Se faltar algum, acrescenta-o primeiro na folha Listas.</t>
+    <t>3. Curso e Entidade escolhem-se da lista. Escola ou curso novo? Acrescenta-o primeiro na folha Listas.</t>
   </si>
   <si>
     <t>4. Para várias pessoas do mesmo curso, preenche o Curso, a Entidade e as datas na primeira linha e arrasta para baixo.</t>
@@ -230,6 +236,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF171412"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <color rgb="FF8A7F75"/>
       <sz val="10"/>
@@ -239,12 +251,6 @@
       <b/>
       <color rgb="FF171412"/>
       <sz val="14"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF171412"/>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -287,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -298,18 +304,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13712,7 +13719,8 @@
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -13742,1212 +13750,1025 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="A8" s="6"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="A9" s="6"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="6"/>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="6"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="6"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="6"/>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="6"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="6"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="6"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="6"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="6"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="6"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="6"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="C25" s="2"/>
+      <c r="A25" s="6"/>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="A26" s="6"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="A27" s="6"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="A28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="A29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="A30" s="6"/>
+      <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="C31" s="2"/>
+      <c r="A31" s="6"/>
+      <c r="C31" s="6"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="A32" s="6"/>
+      <c r="C32" s="6"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="C33" s="2"/>
+      <c r="A33" s="6"/>
+      <c r="C33" s="6"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="A34" s="6"/>
+      <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="A35" s="6"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="C36" s="2"/>
+      <c r="A36" s="6"/>
+      <c r="C36" s="6"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="A37" s="6"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="C38" s="2"/>
+      <c r="A38" s="6"/>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="C39" s="2"/>
+      <c r="A39" s="6"/>
+      <c r="C39" s="6"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="C40" s="2"/>
+      <c r="A40" s="6"/>
+      <c r="C40" s="6"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
-      <c r="C41" s="2"/>
+      <c r="A41" s="6"/>
+      <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
-      <c r="C42" s="2"/>
+      <c r="A42" s="6"/>
+      <c r="C42" s="6"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="C43" s="2"/>
+      <c r="A43" s="6"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
-      <c r="C44" s="2"/>
+      <c r="A44" s="6"/>
+      <c r="C44" s="6"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="C45" s="2"/>
+      <c r="A45" s="6"/>
+      <c r="C45" s="6"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="C46" s="2"/>
+      <c r="A46" s="6"/>
+      <c r="C46" s="6"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="C47" s="2"/>
+      <c r="A47" s="6"/>
+      <c r="C47" s="6"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="C48" s="2"/>
+      <c r="A48" s="6"/>
+      <c r="C48" s="6"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="C49" s="2"/>
+      <c r="A49" s="6"/>
+      <c r="C49" s="6"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
-      <c r="C50" s="2"/>
+      <c r="A50" s="6"/>
+      <c r="C50" s="6"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="C51" s="2"/>
+      <c r="A51" s="6"/>
+      <c r="C51" s="6"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="C52" s="2"/>
+      <c r="A52" s="6"/>
+      <c r="C52" s="6"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="C53" s="2"/>
+      <c r="A53" s="6"/>
+      <c r="C53" s="6"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="C54" s="2"/>
+      <c r="A54" s="6"/>
+      <c r="C54" s="6"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="C55" s="2"/>
+      <c r="A55" s="6"/>
+      <c r="C55" s="6"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="A56" s="6"/>
+      <c r="C56" s="6"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="C57" s="2"/>
+      <c r="A57" s="6"/>
+      <c r="C57" s="6"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="C58" s="2"/>
+      <c r="A58" s="6"/>
+      <c r="C58" s="6"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="C59" s="2"/>
+      <c r="A59" s="6"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="C60" s="2"/>
+      <c r="A60" s="6"/>
+      <c r="C60" s="6"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="C61" s="2"/>
+      <c r="A61" s="6"/>
+      <c r="C61" s="6"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="C62" s="2"/>
+      <c r="A62" s="6"/>
+      <c r="C62" s="6"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="A63" s="6"/>
+      <c r="C63" s="6"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="C64" s="2"/>
+      <c r="A64" s="6"/>
+      <c r="C64" s="6"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="C65" s="2"/>
+      <c r="A65" s="6"/>
+      <c r="C65" s="6"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
-      <c r="C66" s="2"/>
+      <c r="A66" s="6"/>
+      <c r="C66" s="6"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="C67" s="2"/>
+      <c r="A67" s="6"/>
+      <c r="C67" s="6"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
-      <c r="C68" s="2"/>
+      <c r="A68" s="6"/>
+      <c r="C68" s="6"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
-      <c r="C69" s="2"/>
+      <c r="A69" s="6"/>
+      <c r="C69" s="6"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2"/>
-      <c r="C70" s="2"/>
+      <c r="A70" s="6"/>
+      <c r="C70" s="6"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
-      <c r="C71" s="2"/>
+      <c r="A71" s="6"/>
+      <c r="C71" s="6"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2"/>
-      <c r="C72" s="2"/>
+      <c r="A72" s="6"/>
+      <c r="C72" s="6"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2"/>
-      <c r="C73" s="2"/>
+      <c r="A73" s="6"/>
+      <c r="C73" s="6"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2"/>
-      <c r="C74" s="2"/>
+      <c r="A74" s="6"/>
+      <c r="C74" s="6"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2"/>
-      <c r="C75" s="2"/>
+      <c r="A75" s="6"/>
+      <c r="C75" s="6"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
-      <c r="C76" s="2"/>
+      <c r="A76" s="6"/>
+      <c r="C76" s="6"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
-      <c r="C77" s="2"/>
+      <c r="A77" s="6"/>
+      <c r="C77" s="6"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
-      <c r="C78" s="2"/>
+      <c r="A78" s="6"/>
+      <c r="C78" s="6"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2"/>
-      <c r="C79" s="2"/>
+      <c r="A79" s="6"/>
+      <c r="C79" s="6"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
-      <c r="C80" s="2"/>
+      <c r="A80" s="6"/>
+      <c r="C80" s="6"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-      <c r="C81" s="2"/>
+      <c r="A81" s="6"/>
+      <c r="C81" s="6"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
-      <c r="C82" s="2"/>
+      <c r="A82" s="6"/>
+      <c r="C82" s="6"/>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
-      <c r="C83" s="2"/>
+      <c r="A83" s="6"/>
+      <c r="C83" s="6"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
-      <c r="C84" s="2"/>
+      <c r="A84" s="6"/>
+      <c r="C84" s="6"/>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
-      <c r="C85" s="2"/>
+      <c r="A85" s="6"/>
+      <c r="C85" s="6"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
-      <c r="C86" s="2"/>
+      <c r="A86" s="6"/>
+      <c r="C86" s="6"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
-      <c r="C87" s="2"/>
+      <c r="A87" s="6"/>
+      <c r="C87" s="6"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2"/>
-      <c r="C88" s="2"/>
+      <c r="A88" s="6"/>
+      <c r="C88" s="6"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
-      <c r="C89" s="2"/>
+      <c r="A89" s="6"/>
+      <c r="C89" s="6"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
-      <c r="C90" s="2"/>
+      <c r="A90" s="6"/>
+      <c r="C90" s="6"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2"/>
-      <c r="C91" s="2"/>
+      <c r="A91" s="6"/>
+      <c r="C91" s="6"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
-      <c r="C92" s="2"/>
+      <c r="A92" s="6"/>
+      <c r="C92" s="6"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2"/>
-      <c r="C93" s="2"/>
+      <c r="A93" s="6"/>
+      <c r="C93" s="6"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2"/>
-      <c r="C94" s="2"/>
+      <c r="A94" s="6"/>
+      <c r="C94" s="6"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2"/>
-      <c r="C95" s="2"/>
+      <c r="A95" s="6"/>
+      <c r="C95" s="6"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
-      <c r="C96" s="2"/>
+      <c r="A96" s="6"/>
+      <c r="C96" s="6"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2"/>
-      <c r="C97" s="2"/>
+      <c r="A97" s="6"/>
+      <c r="C97" s="6"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
-      <c r="C98" s="2"/>
+      <c r="A98" s="6"/>
+      <c r="C98" s="6"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
-      <c r="C99" s="2"/>
+      <c r="A99" s="6"/>
+      <c r="C99" s="6"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
-      <c r="C100" s="2"/>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2"/>
-      <c r="C101" s="2"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2"/>
-      <c r="C102" s="2"/>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2"/>
-      <c r="C103" s="2"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
-      <c r="C104" s="2"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
-      <c r="C105" s="2"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2"/>
-      <c r="C106" s="2"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2"/>
-      <c r="C107" s="2"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2"/>
-      <c r="C108" s="2"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="C109" s="2"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="C110" s="2"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="C111" s="2"/>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="C112" s="2"/>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="C113" s="2"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="C114" s="2"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="C115" s="2"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="C116" s="2"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="C117" s="2"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="C118" s="2"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="C119" s="2"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
-      <c r="C120" s="2"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="2"/>
-      <c r="C121" s="2"/>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="2"/>
-      <c r="C122" s="2"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2"/>
-      <c r="C123" s="2"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2"/>
-      <c r="C124" s="2"/>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2"/>
-      <c r="C125" s="2"/>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2"/>
-      <c r="C126" s="2"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
-      <c r="C127" s="2"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="2"/>
-      <c r="C128" s="2"/>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="2"/>
-      <c r="C129" s="2"/>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2"/>
-      <c r="C130" s="2"/>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="2"/>
-      <c r="C131" s="2"/>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="2"/>
-      <c r="C132" s="2"/>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
-      <c r="C133" s="2"/>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="2"/>
-      <c r="C134" s="2"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2"/>
-      <c r="C135" s="2"/>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
-      <c r="C136" s="2"/>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="2"/>
-      <c r="C137" s="2"/>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="2"/>
-      <c r="C138" s="2"/>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="2"/>
-      <c r="C139" s="2"/>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="2"/>
-      <c r="C140" s="2"/>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="2"/>
-      <c r="C141" s="2"/>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
-      <c r="C142" s="2"/>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="2"/>
-      <c r="C143" s="2"/>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="2"/>
-      <c r="C144" s="2"/>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="2"/>
-      <c r="C145" s="2"/>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
-      <c r="C146" s="2"/>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="2"/>
-      <c r="C147" s="2"/>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="2"/>
-      <c r="C148" s="2"/>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="2"/>
-      <c r="C149" s="2"/>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="2"/>
-      <c r="C150" s="2"/>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="2"/>
-      <c r="C151" s="2"/>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
-      <c r="C152" s="2"/>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="2"/>
-      <c r="C153" s="2"/>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="2"/>
-      <c r="C154" s="2"/>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="2"/>
-      <c r="C155" s="2"/>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="2"/>
-      <c r="C156" s="2"/>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="2"/>
-      <c r="C157" s="2"/>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="2"/>
-      <c r="C158" s="2"/>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="2"/>
-      <c r="C159" s="2"/>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="2"/>
-      <c r="C160" s="2"/>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="2"/>
-      <c r="C161" s="2"/>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="2"/>
-      <c r="C162" s="2"/>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="2"/>
-      <c r="C163" s="2"/>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="2"/>
-      <c r="C164" s="2"/>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="2"/>
-      <c r="C165" s="2"/>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="2"/>
-      <c r="C166" s="2"/>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="2"/>
-      <c r="C167" s="2"/>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="2"/>
-      <c r="C168" s="2"/>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="2"/>
-      <c r="C169" s="2"/>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="2"/>
-      <c r="C170" s="2"/>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="2"/>
-      <c r="C171" s="2"/>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="2"/>
-      <c r="C172" s="2"/>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="2"/>
-      <c r="C173" s="2"/>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="2"/>
-      <c r="C174" s="2"/>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="2"/>
-      <c r="C175" s="2"/>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="2"/>
-      <c r="C176" s="2"/>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2"/>
-      <c r="C177" s="2"/>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
-      <c r="C178" s="2"/>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="2"/>
-      <c r="C179" s="2"/>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2"/>
-      <c r="C180" s="2"/>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="2"/>
-      <c r="C181" s="2"/>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="2"/>
-      <c r="C182" s="2"/>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="2"/>
-      <c r="C183" s="2"/>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="2"/>
-      <c r="C184" s="2"/>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="2"/>
-      <c r="C185" s="2"/>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="2"/>
-      <c r="C186" s="2"/>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="2"/>
-      <c r="C187" s="2"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="2"/>
-      <c r="C188" s="2"/>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="2"/>
-      <c r="C189" s="2"/>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="2"/>
-      <c r="C190" s="2"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="2"/>
-      <c r="C191" s="2"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="2"/>
-      <c r="C192" s="2"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="2"/>
-      <c r="C193" s="2"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="2"/>
-      <c r="C194" s="2"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="2"/>
-      <c r="C195" s="2"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="2"/>
-      <c r="C196" s="2"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="2"/>
-      <c r="C197" s="2"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="2"/>
-      <c r="C198" s="2"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="2"/>
-      <c r="C199" s="2"/>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="2"/>
-      <c r="C200" s="2"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="2"/>
-      <c r="C201" s="2"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="2"/>
-      <c r="C202" s="2"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="2"/>
-      <c r="C203" s="2"/>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="C204" s="2"/>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="C205" s="2"/>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="2"/>
-      <c r="C206" s="2"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="2"/>
-      <c r="C207" s="2"/>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="2"/>
-      <c r="C208" s="2"/>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="2"/>
-      <c r="C209" s="2"/>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="2"/>
-      <c r="C210" s="2"/>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="2"/>
-      <c r="C211" s="2"/>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="2"/>
-      <c r="C212" s="2"/>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="2"/>
-      <c r="C213" s="2"/>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="2"/>
-      <c r="C214" s="2"/>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="2"/>
-      <c r="C215" s="2"/>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="2"/>
-      <c r="C216" s="2"/>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="2"/>
-      <c r="C217" s="2"/>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="2"/>
-      <c r="C218" s="2"/>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="2"/>
-      <c r="C219" s="2"/>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="2"/>
-      <c r="C220" s="2"/>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="2"/>
-      <c r="C221" s="2"/>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="2"/>
-      <c r="C222" s="2"/>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="2"/>
-      <c r="C223" s="2"/>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="2"/>
-      <c r="C224" s="2"/>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="2"/>
-      <c r="C225" s="2"/>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="2"/>
-      <c r="C226" s="2"/>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="2"/>
-      <c r="C227" s="2"/>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="2"/>
-      <c r="C228" s="2"/>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="2"/>
-      <c r="C229" s="2"/>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="2"/>
-      <c r="C230" s="2"/>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="2"/>
-      <c r="C231" s="2"/>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="2"/>
-      <c r="C232" s="2"/>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A233" s="2"/>
-      <c r="C233" s="2"/>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A234" s="2"/>
-      <c r="C234" s="2"/>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A235" s="2"/>
-      <c r="C235" s="2"/>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="2"/>
-      <c r="C236" s="2"/>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="2"/>
-      <c r="C237" s="2"/>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="2"/>
-      <c r="C238" s="2"/>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A239" s="2"/>
-      <c r="C239" s="2"/>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A240" s="2"/>
-      <c r="C240" s="2"/>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A241" s="2"/>
-      <c r="C241" s="2"/>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A242" s="2"/>
-      <c r="C242" s="2"/>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A243" s="2"/>
-      <c r="C243" s="2"/>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A244" s="2"/>
-      <c r="C244" s="2"/>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A245" s="2"/>
-      <c r="C245" s="2"/>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A246" s="2"/>
-      <c r="C246" s="2"/>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A247" s="2"/>
-      <c r="C247" s="2"/>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" s="2"/>
-      <c r="C248" s="2"/>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A249" s="2"/>
-      <c r="C249" s="2"/>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A250" s="2"/>
-      <c r="C250" s="2"/>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A251" s="2"/>
-      <c r="C251" s="2"/>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A252" s="2"/>
-      <c r="C252" s="2"/>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A253" s="2"/>
-      <c r="C253" s="2"/>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A254" s="2"/>
-      <c r="C254" s="2"/>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A255" s="2"/>
-      <c r="C255" s="2"/>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A256" s="2"/>
-      <c r="C256" s="2"/>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" s="2"/>
-      <c r="C257" s="2"/>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A258" s="2"/>
-      <c r="C258" s="2"/>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A259" s="2"/>
-      <c r="C259" s="2"/>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" s="2"/>
-      <c r="C260" s="2"/>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" s="2"/>
-      <c r="C261" s="2"/>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A262" s="2"/>
-      <c r="C262" s="2"/>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A263" s="2"/>
-      <c r="C263" s="2"/>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A264" s="2"/>
-      <c r="C264" s="2"/>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A265" s="2"/>
-      <c r="C265" s="2"/>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A266" s="2"/>
-      <c r="C266" s="2"/>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A267" s="2"/>
-      <c r="C267" s="2"/>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A268" s="2"/>
-      <c r="C268" s="2"/>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A269" s="2"/>
-      <c r="C269" s="2"/>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A270" s="2"/>
-      <c r="C270" s="2"/>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A271" s="2"/>
-      <c r="C271" s="2"/>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A272" s="2"/>
-      <c r="C272" s="2"/>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A273" s="2"/>
-      <c r="C273" s="2"/>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A274" s="2"/>
-      <c r="C274" s="2"/>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A275" s="2"/>
-      <c r="C275" s="2"/>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A276" s="2"/>
-      <c r="C276" s="2"/>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A277" s="2"/>
-      <c r="C277" s="2"/>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A278" s="2"/>
-      <c r="C278" s="2"/>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A279" s="2"/>
-      <c r="C279" s="2"/>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A280" s="2"/>
-      <c r="C280" s="2"/>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A281" s="2"/>
-      <c r="C281" s="2"/>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A282" s="2"/>
-      <c r="C282" s="2"/>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A283" s="2"/>
-      <c r="C283" s="2"/>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A284" s="2"/>
-      <c r="C284" s="2"/>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A285" s="2"/>
-      <c r="C285" s="2"/>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A286" s="2"/>
-      <c r="C286" s="2"/>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A287" s="2"/>
-      <c r="C287" s="2"/>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A288" s="2"/>
-      <c r="C288" s="2"/>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A289" s="2"/>
-      <c r="C289" s="2"/>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A290" s="2"/>
-      <c r="C290" s="2"/>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A291" s="2"/>
-      <c r="C291" s="2"/>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A292" s="2"/>
-      <c r="C292" s="2"/>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A293" s="2"/>
-      <c r="C293" s="2"/>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A294" s="2"/>
-      <c r="C294" s="2"/>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A295" s="2"/>
-      <c r="C295" s="2"/>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A296" s="2"/>
-      <c r="C296" s="2"/>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A297" s="2"/>
-      <c r="C297" s="2"/>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A298" s="2"/>
-      <c r="C298" s="2"/>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A299" s="2"/>
-      <c r="C299" s="2"/>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A300" s="2"/>
-      <c r="C300" s="2"/>
+      <c r="A100" s="6"/>
+      <c r="C100" s="6"/>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C101" s="6"/>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C102" s="6"/>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C103" s="6"/>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C104" s="6"/>
+    </row>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C105" s="6"/>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C106" s="6"/>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C107" s="6"/>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C108" s="6"/>
+    </row>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C109" s="6"/>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C110" s="6"/>
+    </row>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C111" s="6"/>
+    </row>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C112" s="6"/>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C113" s="6"/>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C114" s="6"/>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C115" s="6"/>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C116" s="6"/>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C117" s="6"/>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C118" s="6"/>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C119" s="6"/>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C120" s="6"/>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C121" s="6"/>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C122" s="6"/>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C123" s="6"/>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C124" s="6"/>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C125" s="6"/>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C126" s="6"/>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C127" s="6"/>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C128" s="6"/>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C129" s="6"/>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C130" s="6"/>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C131" s="6"/>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C132" s="6"/>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C133" s="6"/>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C134" s="6"/>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C135" s="6"/>
+    </row>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C136" s="6"/>
+    </row>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C137" s="6"/>
+    </row>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C138" s="6"/>
+    </row>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C139" s="6"/>
+    </row>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C140" s="6"/>
+    </row>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C141" s="6"/>
+    </row>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C142" s="6"/>
+    </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C143" s="6"/>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C144" s="6"/>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C145" s="6"/>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C146" s="6"/>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C147" s="6"/>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C148" s="6"/>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C149" s="6"/>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C150" s="6"/>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C151" s="6"/>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C152" s="6"/>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C153" s="6"/>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C154" s="6"/>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C155" s="6"/>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C156" s="6"/>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C157" s="6"/>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C158" s="6"/>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C159" s="6"/>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C160" s="6"/>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="6"/>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="6"/>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C163" s="6"/>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C164" s="6"/>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="6"/>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C166" s="6"/>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C167" s="6"/>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="6"/>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C169" s="6"/>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C170" s="6"/>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C171" s="6"/>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C172" s="6"/>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C173" s="6"/>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C174" s="6"/>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C175" s="6"/>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C176" s="6"/>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C177" s="6"/>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C178" s="6"/>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C179" s="6"/>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C180" s="6"/>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C181" s="6"/>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C182" s="6"/>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C183" s="6"/>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C184" s="6"/>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C185" s="6"/>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C186" s="6"/>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C187" s="6"/>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C188" s="6"/>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C189" s="6"/>
+    </row>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C190" s="6"/>
+    </row>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C191" s="6"/>
+    </row>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C192" s="6"/>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C193" s="6"/>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C194" s="6"/>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C195" s="6"/>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C196" s="6"/>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C197" s="6"/>
+    </row>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C198" s="6"/>
+    </row>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C199" s="6"/>
+    </row>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C200" s="6"/>
+    </row>
+    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C201" s="6"/>
+    </row>
+    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C202" s="6"/>
+    </row>
+    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C203" s="6"/>
+    </row>
+    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C204" s="6"/>
+    </row>
+    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C205" s="6"/>
+    </row>
+    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C206" s="6"/>
+    </row>
+    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C207" s="6"/>
+    </row>
+    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C208" s="6"/>
+    </row>
+    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C209" s="6"/>
+    </row>
+    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C210" s="6"/>
+    </row>
+    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C211" s="6"/>
+    </row>
+    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C212" s="6"/>
+    </row>
+    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C213" s="6"/>
+    </row>
+    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C214" s="6"/>
+    </row>
+    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C215" s="6"/>
+    </row>
+    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C216" s="6"/>
+    </row>
+    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C217" s="6"/>
+    </row>
+    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C218" s="6"/>
+    </row>
+    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C219" s="6"/>
+    </row>
+    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C220" s="6"/>
+    </row>
+    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C221" s="6"/>
+    </row>
+    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C222" s="6"/>
+    </row>
+    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C223" s="6"/>
+    </row>
+    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C224" s="6"/>
+    </row>
+    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C225" s="6"/>
+    </row>
+    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C226" s="6"/>
+    </row>
+    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C227" s="6"/>
+    </row>
+    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C228" s="6"/>
+    </row>
+    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C229" s="6"/>
+    </row>
+    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C230" s="6"/>
+    </row>
+    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C231" s="6"/>
+    </row>
+    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C232" s="6"/>
+    </row>
+    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C233" s="6"/>
+    </row>
+    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C234" s="6"/>
+    </row>
+    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C235" s="6"/>
+    </row>
+    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C236" s="6"/>
+    </row>
+    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C237" s="6"/>
+    </row>
+    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C238" s="6"/>
+    </row>
+    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C239" s="6"/>
+    </row>
+    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C240" s="6"/>
+    </row>
+    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C241" s="6"/>
+    </row>
+    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C242" s="6"/>
+    </row>
+    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C243" s="6"/>
+    </row>
+    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C244" s="6"/>
+    </row>
+    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C245" s="6"/>
+    </row>
+    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C246" s="6"/>
+    </row>
+    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C247" s="6"/>
+    </row>
+    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C248" s="6"/>
+    </row>
+    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C249" s="6"/>
+    </row>
+    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C250" s="6"/>
+    </row>
+    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C251" s="6"/>
+    </row>
+    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C252" s="6"/>
+    </row>
+    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C253" s="6"/>
+    </row>
+    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C254" s="6"/>
+    </row>
+    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C255" s="6"/>
+    </row>
+    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C256" s="6"/>
+    </row>
+    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C257" s="6"/>
+    </row>
+    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C258" s="6"/>
+    </row>
+    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C259" s="6"/>
+    </row>
+    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C260" s="6"/>
+    </row>
+    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C261" s="6"/>
+    </row>
+    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C262" s="6"/>
+    </row>
+    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C263" s="6"/>
+    </row>
+    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C264" s="6"/>
+    </row>
+    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C265" s="6"/>
+    </row>
+    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C266" s="6"/>
+    </row>
+    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C267" s="6"/>
+    </row>
+    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C268" s="6"/>
+    </row>
+    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C269" s="6"/>
+    </row>
+    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C270" s="6"/>
+    </row>
+    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C271" s="6"/>
+    </row>
+    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C272" s="6"/>
+    </row>
+    <row r="273" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C273" s="6"/>
+    </row>
+    <row r="274" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C274" s="6"/>
+    </row>
+    <row r="275" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C275" s="6"/>
+    </row>
+    <row r="276" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C276" s="6"/>
+    </row>
+    <row r="277" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C277" s="6"/>
+    </row>
+    <row r="278" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C278" s="6"/>
+    </row>
+    <row r="279" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C279" s="6"/>
+    </row>
+    <row r="280" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C280" s="6"/>
+    </row>
+    <row r="281" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C281" s="6"/>
+    </row>
+    <row r="282" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C282" s="6"/>
+    </row>
+    <row r="283" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C283" s="6"/>
+    </row>
+    <row r="284" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C284" s="6"/>
+    </row>
+    <row r="285" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C285" s="6"/>
+    </row>
+    <row r="286" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C286" s="6"/>
+    </row>
+    <row r="287" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C287" s="6"/>
+    </row>
+    <row r="288" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C288" s="6"/>
+    </row>
+    <row r="289" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C289" s="6"/>
+    </row>
+    <row r="290" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C290" s="6"/>
+    </row>
+    <row r="291" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C291" s="6"/>
+    </row>
+    <row r="292" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C292" s="6"/>
+    </row>
+    <row r="293" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C293" s="6"/>
+    </row>
+    <row r="294" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C294" s="6"/>
+    </row>
+    <row r="295" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C295" s="6"/>
+    </row>
+    <row r="296" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C296" s="6"/>
+    </row>
+    <row r="297" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C297" s="6"/>
+    </row>
+    <row r="298" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C298" s="6"/>
+    </row>
+    <row r="299" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C299" s="6"/>
+    </row>
+    <row r="300" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C300" s="6"/>
     </row>
   </sheetData>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -14969,176 +14790,176 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="12">
         <v>46279</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="12">
         <v>46325</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+      <c r="I15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -15153,6 +14974,7 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B17:I17"/>
   </mergeCells>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/repo/modelo-formandos.xlsx
+++ b/repo/modelo-formandos.xlsx
@@ -31,7 +31,7 @@
             <sz val="9"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Obrigatório. Só o primeiro nome, ou os nomes próprios.</t>
+          <t>Obrigatório. Podes colar aqui o nome completo, mesmo em maiúsculas, e deixar o Apelido em branco: o Repo parte-o e acerta-o ao carregar.</t>
         </r>
       </text>
     </comment>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>Nome</t>
   </si>
@@ -182,10 +182,13 @@
     <t>4. Para várias pessoas do mesmo curso, preenche o Curso, a Entidade e as datas na primeira linha e arrasta para baixo.</t>
   </si>
   <si>
-    <t>5. Pode ser uma formação por ficheiro ou todas no mesmo. Os dois funcionam.</t>
+    <t>5. Se a lista tem o nome completo numa só coluna (como as do IEFP), cola-o todo no Nome e deixa o Apelido em branco. Maiúsculas não fazem mal: o Repo parte o nome e acerta-o ao carregar.</t>
   </si>
   <si>
-    <t>6. Grava como .xlsx e carrega no Repo, em Formandos.</t>
+    <t>6. Pode ser uma formação por ficheiro ou todas no mesmo. Os dois funcionam.</t>
+  </si>
+  <si>
+    <t>7. Grava como .xlsx e carrega no Repo, em Formandos.</t>
   </si>
   <si>
     <t>Obrigatórios: Nome, Email, Curso, Entidade. O resto ajuda, mas pode ficar em branco.</t>
@@ -14777,7 +14780,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I17"/>
+  <dimension ref="B2:I18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -14873,96 +14876,108 @@
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C15" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E15" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H15" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I15" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="11" t="s">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="C16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="D16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G16" s="12">
         <v>46279</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H16" s="12">
         <v>46325</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="I16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:I5"/>
@@ -14970,9 +14985,10 @@
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B18:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>

--- a/repo/modelo-formandos.xlsx
+++ b/repo/modelo-formandos.xlsx
@@ -86,7 +86,7 @@
             <sz val="9"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Data de início da formação, dd/mm/aaaa.</t>
+          <t>O mês da turma. Basta o mês: escreve 01/2026 ou janeiro 2026.</t>
         </r>
       </text>
     </comment>
@@ -97,7 +97,7 @@
             <sz val="9"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Data de fim. Opcional.</t>
+          <t>Opcional. O mês em que acabou, se não for o mesmo do início.</t>
         </r>
       </text>
     </comment>
@@ -217,7 +217,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -670,7 +670,7 @@
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="6" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="36" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14788,7 +14788,7 @@
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14955,10 +14955,10 @@
         <v>11</v>
       </c>
       <c r="G16" s="12">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="H16" s="12">
-        <v>46325</v>
+        <v>46296</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>29</v>
